--- a/results/009_final_results/009_final_model_comparison.xlsx
+++ b/results/009_final_results/009_final_model_comparison.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,30 +442,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>MAE_std</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>RMSE_std</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>R2_std</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
@@ -474,148 +459,376 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Random Forest — All Features</t>
+          <t>Global Mean</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>373.7910621232759</v>
+        <v>732.1123603603603</v>
       </c>
       <c r="C2" t="n">
-        <v>94.39703488126128</v>
+        <v>898.7328565068274</v>
       </c>
       <c r="D2" t="n">
-        <v>563.8098814943988</v>
-      </c>
-      <c r="E2" t="n">
-        <v>154.0265649012071</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.438064813368267</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.1636527315710693</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Walk-forward validation</t>
+        <v>-0.1043772529447408</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7-Day Mean</t>
+          <t>User Mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>366.4455002665644</v>
+        <v>486.7906666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>98.6326300290702</v>
+        <v>753.1805972501377</v>
       </c>
       <c r="D3" t="n">
-        <v>566.3899122991439</v>
-      </c>
-      <c r="E3" t="n">
-        <v>166.422798578068</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.4324715565191854</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1890181624067264</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Walk-forward validation</t>
+        <v>0.2243702445357214</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>User Mean</t>
+          <t>Previous Day</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>367.93592284344</v>
+        <v>542.432</v>
       </c>
       <c r="C4" t="n">
-        <v>102.940977481292</v>
+        <v>803.8786177029465</v>
       </c>
       <c r="D4" t="n">
-        <v>572.8225940867585</v>
-      </c>
-      <c r="E4" t="n">
-        <v>156.4972853196723</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.4198694585944822</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.1693263450399319</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Walk-forward validation</t>
+        <v>0.1164377174065655</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Linear Regression — Base</t>
+          <t>7-Day Mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>389.7171215600611</v>
+        <v>479.9668571428573</v>
       </c>
       <c r="C5" t="n">
-        <v>92.34654561843161</v>
+        <v>757.968226031586</v>
       </c>
       <c r="D5" t="n">
-        <v>576.5765708205211</v>
-      </c>
-      <c r="E5" t="n">
-        <v>141.1027110459971</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.4123999073488727</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.137670637866248</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Walk-forward validation</t>
+        <v>0.2144782487923939</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Linear Regression — Base</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>496.0380794019032</v>
+      </c>
+      <c r="C6" t="n">
+        <v>738.5981202261911</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2541137342869998</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Decision Tree — Base</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
+        <v>496.2133975016243</v>
+      </c>
+      <c r="C7" t="n">
+        <v>719.3815608998336</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2924211907747984</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Linear Regression — Lag</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>503.1245093622542</v>
+      </c>
+      <c r="C8" t="n">
+        <v>760.2356814145672</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2097714561124187</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Decision Tree — Lag</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>566.1333934988944</v>
+      </c>
+      <c r="C9" t="n">
+        <v>784.007619270227</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1595792220552865</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Linear Regression — Rolling</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>492.4568996426653</v>
+      </c>
+      <c r="C10" t="n">
+        <v>758.8200375728881</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2127117038365232</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Decision Tree — Rolling</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>517.990044802584</v>
+      </c>
+      <c r="C11" t="n">
+        <v>787.8379357833979</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1513473094990588</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Linear Regression — All Features</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>485.0493597101472</v>
+      </c>
+      <c r="C12" t="n">
+        <v>754.3263048952043</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2220087370060092</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Decision Tree — All Features</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>533.4940521368898</v>
+      </c>
+      <c r="C13" t="n">
+        <v>789.1612508821314</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1484939864052046</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Random Forest — All Features</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>481.7334122956305</v>
+      </c>
+      <c r="C14" t="n">
+        <v>740.4334498547873</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2504022490773984</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Single train/test split</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Random Forest — All Features</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>373.7910621232759</v>
+      </c>
+      <c r="C15" t="n">
+        <v>563.8098814943988</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.438064813368267</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Walk-forward validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7-Day Mean</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>366.4455002665644</v>
+      </c>
+      <c r="C16" t="n">
+        <v>566.3899122991439</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4324715565191854</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Walk-forward validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>User Mean</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>367.93592284344</v>
+      </c>
+      <c r="C17" t="n">
+        <v>572.8225940867585</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4198694585944822</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Walk-forward validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Linear Regression — Base</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>389.7171215600611</v>
+      </c>
+      <c r="C18" t="n">
+        <v>576.5765708205211</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4123999073488727</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Walk-forward validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Decision Tree — Base</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>404.6027102845257</v>
       </c>
-      <c r="C6" t="n">
-        <v>81.05177096834066</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C19" t="n">
         <v>582.5245371353326</v>
       </c>
-      <c r="E6" t="n">
-        <v>121.545113449311</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D19" t="n">
         <v>0.3992443735245514</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.1000775158483923</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Walk-forward validation</t>
         </is>
